--- a/Excel/PracticeExcel/03PivotTables/sample-data-pivots-blank 1.xlsx
+++ b/Excel/PracticeExcel/03PivotTables/sample-data-pivots-blank 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell 7490\Desktop\PythonLibraries\PythonJupitarNotebook\Excel\PracticeExcel\03PivotTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B4A1F2-B7A0-4CC7-9D79-BED42CA4DE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9564D9AB-4766-4322-8B28-20F4E3767CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="882" activeTab="3" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="882" activeTab="2" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivots" sheetId="1" r:id="rId1"/>
